--- a/Marketing.xlsx
+++ b/Marketing.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F61C8EF785657325EE6CE6285FDD0CD5905ED145" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B09FC8FB-73F4-4532-89D1-F966BCE14AAF}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJET\flora\mon-premier-projet-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A3E2B9-767F-4E2F-950B-49C842CE0133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marketing" sheetId="1" r:id="rId1"/>
@@ -499,7 +504,7 @@
     <numFmt numFmtId="165" formatCode="d\.m"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -569,7 +574,333 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -580,6 +911,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BFAD897E-9A5F-461C-9977-99A462AC65A2}" name="Tableau1" displayName="Tableau1" ref="A1:P106" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:P106" xr:uid="{BFAD897E-9A5F-461C-9977-99A462AC65A2}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{D43126BF-1330-4332-80FA-6D31D6C328FB}" name="Date" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{52FD911D-8389-4B0A-93EA-B92E49C54A1C}" name="Canal" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{58D64AB9-168B-4033-B79F-F0BAAD8F15BD}" name="Campagne" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{B0480456-B210-4128-A6F3-E61F4ECE9310}" name="Région" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{1A1B5CCC-A666-41E4-A570-E2483C023DB3}" name="Device" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{5953CAE6-7666-46A5-8D82-93FA13EEBB19}" name="Impressions" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{0545F767-ABB2-4D3F-AF87-0ECE4F4A6804}" name="Clicks" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{645B27C1-A2BE-4291-BD2D-65BBC570A069}" name="CTR" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{185BEFFA-1A43-4CA1-9088-DC247300EC72}" name="CPC" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{43ADC8EB-9820-4E50-A9AE-DAE842F06A9F}" name="Spend" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{CF765D8D-AFB7-4E13-8143-48BC1E7ED1DA}" name="Sessions" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{36F0D2B6-6C7F-4A47-B711-7375E7A9E9AB}" name="Leads" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{498062BF-9363-4A57-96E9-908FD1DEC2DA}" name="Conversions" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{9E0EED2E-6A7E-49EF-B8FB-59A92B1FC585}" name="Revenue" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{287458DD-97F0-4150-A42B-B70600731C09}" name="ROAS" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{B97C1BE8-D7CF-47EC-AC2E-67C5BB1BF9BD}" name="Bounce Rate" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -784,12 +1140,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z106"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.08984375" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" customWidth="1"/>
+    <col min="13" max="13" width="13.6328125" customWidth="1"/>
+    <col min="16" max="16" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +1209,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45658</v>
       </c>
@@ -899,7 +1259,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45659</v>
       </c>
@@ -949,7 +1309,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45660</v>
       </c>
@@ -999,7 +1359,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45661</v>
       </c>
@@ -1049,7 +1409,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45662</v>
       </c>
@@ -1099,7 +1459,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45663</v>
       </c>
@@ -1149,7 +1509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45664</v>
       </c>
@@ -1199,7 +1559,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45665</v>
       </c>
@@ -1249,7 +1609,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45666</v>
       </c>
@@ -1299,7 +1659,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45667</v>
       </c>
@@ -1349,7 +1709,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45668</v>
       </c>
@@ -1399,7 +1759,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45669</v>
       </c>
@@ -1449,7 +1809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45670</v>
       </c>
@@ -1499,7 +1859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45671</v>
       </c>
@@ -1549,7 +1909,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45672</v>
       </c>
@@ -1599,7 +1959,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45673</v>
       </c>
@@ -1649,7 +2009,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45674</v>
       </c>
@@ -1699,7 +2059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45675</v>
       </c>
@@ -1749,7 +2109,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45676</v>
       </c>
@@ -1799,7 +2159,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45677</v>
       </c>
@@ -1849,7 +2209,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45678</v>
       </c>
@@ -1899,7 +2259,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45679</v>
       </c>
@@ -1949,7 +2309,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45680</v>
       </c>
@@ -1999,7 +2359,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45681</v>
       </c>
@@ -2049,7 +2409,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45682</v>
       </c>
@@ -2099,7 +2459,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45683</v>
       </c>
@@ -2149,7 +2509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45684</v>
       </c>
@@ -2199,7 +2559,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45685</v>
       </c>
@@ -2249,7 +2609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45686</v>
       </c>
@@ -2299,7 +2659,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45687</v>
       </c>
@@ -2349,7 +2709,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45688</v>
       </c>
@@ -2399,7 +2759,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45689</v>
       </c>
@@ -2449,7 +2809,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45690</v>
       </c>
@@ -2499,7 +2859,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45691</v>
       </c>
@@ -2549,7 +2909,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45692</v>
       </c>
@@ -2599,7 +2959,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45693</v>
       </c>
@@ -2649,7 +3009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45694</v>
       </c>
@@ -2699,7 +3059,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45695</v>
       </c>
@@ -2749,7 +3109,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45696</v>
       </c>
@@ -2799,7 +3159,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45697</v>
       </c>
@@ -2849,7 +3209,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45698</v>
       </c>
@@ -2899,7 +3259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45699</v>
       </c>
@@ -2949,7 +3309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45700</v>
       </c>
@@ -2999,7 +3359,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45701</v>
       </c>
@@ -3049,7 +3409,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45702</v>
       </c>
@@ -3099,7 +3459,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45703</v>
       </c>
@@ -3149,7 +3509,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45704</v>
       </c>
@@ -3199,7 +3559,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45705</v>
       </c>
@@ -3249,7 +3609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45706</v>
       </c>
@@ -3299,7 +3659,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45707</v>
       </c>
@@ -3349,7 +3709,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45708</v>
       </c>
@@ -3399,7 +3759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45709</v>
       </c>
@@ -3449,7 +3809,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45710</v>
       </c>
@@ -3499,7 +3859,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45711</v>
       </c>
@@ -3549,7 +3909,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45712</v>
       </c>
@@ -3599,7 +3959,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45713</v>
       </c>
@@ -3649,7 +4009,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45714</v>
       </c>
@@ -3699,7 +4059,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45715</v>
       </c>
@@ -3749,7 +4109,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45716</v>
       </c>
@@ -3799,7 +4159,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45717</v>
       </c>
@@ -3849,7 +4209,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45718</v>
       </c>
@@ -3899,7 +4259,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45719</v>
       </c>
@@ -3949,7 +4309,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45720</v>
       </c>
@@ -3999,7 +4359,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45721</v>
       </c>
@@ -4049,7 +4409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45722</v>
       </c>
@@ -4099,7 +4459,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45723</v>
       </c>
@@ -4149,7 +4509,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45724</v>
       </c>
@@ -4199,7 +4559,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45725</v>
       </c>
@@ -4249,7 +4609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45726</v>
       </c>
@@ -4299,7 +4659,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45727</v>
       </c>
@@ -4349,7 +4709,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45728</v>
       </c>
@@ -4399,7 +4759,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>45729</v>
       </c>
@@ -4449,7 +4809,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>45730</v>
       </c>
@@ -4499,7 +4859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>45731</v>
       </c>
@@ -4549,7 +4909,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>45732</v>
       </c>
@@ -4599,7 +4959,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>45733</v>
       </c>
@@ -4649,7 +5009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>45734</v>
       </c>
@@ -4699,7 +5059,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>45735</v>
       </c>
@@ -4749,7 +5109,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>45736</v>
       </c>
@@ -4799,7 +5159,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>45737</v>
       </c>
@@ -4849,7 +5209,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>45738</v>
       </c>
@@ -4899,7 +5259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>45739</v>
       </c>
@@ -4949,7 +5309,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>45740</v>
       </c>
@@ -4999,7 +5359,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>45741</v>
       </c>
@@ -5049,7 +5409,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>45742</v>
       </c>
@@ -5099,7 +5459,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>45743</v>
       </c>
@@ -5149,7 +5509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45744</v>
       </c>
@@ -5199,7 +5559,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>45745</v>
       </c>
@@ -5249,7 +5609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>45746</v>
       </c>
@@ -5299,7 +5659,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>45747</v>
       </c>
@@ -5349,7 +5709,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>45748</v>
       </c>
@@ -5399,7 +5759,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>45749</v>
       </c>
@@ -5449,7 +5809,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>45750</v>
       </c>
@@ -5499,7 +5859,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>45751</v>
       </c>
@@ -5549,7 +5909,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>45752</v>
       </c>
@@ -5599,7 +5959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>45753</v>
       </c>
@@ -5649,7 +6009,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>45754</v>
       </c>
@@ -5699,7 +6059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>45755</v>
       </c>
@@ -5749,7 +6109,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>45756</v>
       </c>
@@ -5799,7 +6159,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>45757</v>
       </c>
@@ -5849,7 +6209,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>45758</v>
       </c>
@@ -5899,7 +6259,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>45759</v>
       </c>
@@ -5949,7 +6309,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>45760</v>
       </c>
@@ -5999,7 +6359,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>45761</v>
       </c>
@@ -6049,7 +6409,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>45762</v>
       </c>
@@ -6101,6 +6461,9 @@
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6110,13 +6473,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>134</v>
       </c>
@@ -6124,7 +6487,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -6132,7 +6495,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
@@ -6140,7 +6503,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -6148,7 +6511,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
@@ -6156,7 +6519,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
@@ -6164,7 +6527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
@@ -6172,7 +6535,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
@@ -6180,7 +6543,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>7</v>
       </c>
@@ -6188,7 +6551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>8</v>
       </c>
@@ -6196,7 +6559,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>9</v>
       </c>
@@ -6204,7 +6567,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
@@ -6212,7 +6575,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
@@ -6220,7 +6583,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>12</v>
       </c>
@@ -6228,7 +6591,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
@@ -6236,7 +6599,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>14</v>
       </c>
@@ -6244,7 +6607,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
@@ -6420,12 +6783,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6434,14 +6791,43 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0705E85-70FB-4344-851D-558E56761DAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0705E85-70FB-4344-851D-558E56761DAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a2709fa8-1d4e-4c7f-b6c7-a29d6af3cec1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F0855DB-26FE-4804-836B-D76131A36494}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302A03C7-5B97-4B6F-B8E0-8596DE798D1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302A03C7-5B97-4B6F-B8E0-8596DE798D1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F0855DB-26FE-4804-836B-D76131A36494}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Marketing.xlsx
+++ b/Marketing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJET\flora\mon-premier-projet-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJET\flora\mon-premier-projet-main\mon-premier-projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A3E2B9-767F-4E2F-950B-49C842CE0133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB98759C-641C-4AE5-A666-77A5BBE897DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marketing" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="154">
   <si>
     <t>Date</t>
   </si>
@@ -493,6 +493,12 @@
   </si>
   <si>
     <t>Taux de rebond</t>
+  </si>
+  <si>
+    <t>CPA</t>
+  </si>
+  <si>
+    <t>coût par acquisition</t>
   </si>
 </sst>
 </file>
@@ -575,42 +581,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -900,6 +870,42 @@
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -914,25 +920,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BFAD897E-9A5F-461C-9977-99A462AC65A2}" name="Tableau1" displayName="Tableau1" ref="A1:P106" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BFAD897E-9A5F-461C-9977-99A462AC65A2}" name="Tableau1" displayName="Tableau1" ref="A1:P106" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:P106" xr:uid="{BFAD897E-9A5F-461C-9977-99A462AC65A2}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D43126BF-1330-4332-80FA-6D31D6C328FB}" name="Date" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{52FD911D-8389-4B0A-93EA-B92E49C54A1C}" name="Canal" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{58D64AB9-168B-4033-B79F-F0BAAD8F15BD}" name="Campagne" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{B0480456-B210-4128-A6F3-E61F4ECE9310}" name="Région" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{1A1B5CCC-A666-41E4-A570-E2483C023DB3}" name="Device" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{5953CAE6-7666-46A5-8D82-93FA13EEBB19}" name="Impressions" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{0545F767-ABB2-4D3F-AF87-0ECE4F4A6804}" name="Clicks" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{645B27C1-A2BE-4291-BD2D-65BBC570A069}" name="CTR" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{185BEFFA-1A43-4CA1-9088-DC247300EC72}" name="CPC" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{43ADC8EB-9820-4E50-A9AE-DAE842F06A9F}" name="Spend" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{CF765D8D-AFB7-4E13-8143-48BC1E7ED1DA}" name="Sessions" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{36F0D2B6-6C7F-4A47-B711-7375E7A9E9AB}" name="Leads" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{498062BF-9363-4A57-96E9-908FD1DEC2DA}" name="Conversions" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{9E0EED2E-6A7E-49EF-B8FB-59A92B1FC585}" name="Revenue" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{287458DD-97F0-4150-A42B-B70600731C09}" name="ROAS" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{B97C1BE8-D7CF-47EC-AC2E-67C5BB1BF9BD}" name="Bounce Rate" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{D43126BF-1330-4332-80FA-6D31D6C328FB}" name="Date" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{52FD911D-8389-4B0A-93EA-B92E49C54A1C}" name="Canal" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{58D64AB9-168B-4033-B79F-F0BAAD8F15BD}" name="Campagne" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{B0480456-B210-4128-A6F3-E61F4ECE9310}" name="Région" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{1A1B5CCC-A666-41E4-A570-E2483C023DB3}" name="Device" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{5953CAE6-7666-46A5-8D82-93FA13EEBB19}" name="Impressions" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{0545F767-ABB2-4D3F-AF87-0ECE4F4A6804}" name="Clicks" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{645B27C1-A2BE-4291-BD2D-65BBC570A069}" name="CTR" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{185BEFFA-1A43-4CA1-9088-DC247300EC72}" name="CPC" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{43ADC8EB-9820-4E50-A9AE-DAE842F06A9F}" name="Spend" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{CF765D8D-AFB7-4E13-8143-48BC1E7ED1DA}" name="Sessions" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{36F0D2B6-6C7F-4A47-B711-7375E7A9E9AB}" name="Leads" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{498062BF-9363-4A57-96E9-908FD1DEC2DA}" name="Conversions" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{9E0EED2E-6A7E-49EF-B8FB-59A92B1FC585}" name="Revenue" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{287458DD-97F0-4150-A42B-B70600731C09}" name="ROAS" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{B97C1BE8-D7CF-47EC-AC2E-67C5BB1BF9BD}" name="Bounce Rate" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1149,7 +1155,7 @@
     <col min="16" max="16" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6472,14 +6478,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.81640625" customWidth="1"/>
     <col min="2" max="2" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>134</v>
       </c>
@@ -6613,6 +6619,14 @@
       </c>
       <c r="B17" s="9" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -6621,6 +6635,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100605B1DFED136D94492CE120B22EC5B2D" ma:contentTypeVersion="7" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="b45ed5dcd277d57d7bc30d9a1e20e8a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a2709fa8-1d4e-4c7f-b6c7-a29d6af3cec1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef33d4839a6e01667a250ebb453ddf1c" ns2:_="">
     <xsd:import namespace="a2709fa8-1d4e-4c7f-b6c7-a29d6af3cec1"/>
@@ -6782,22 +6811,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F0855DB-26FE-4804-836B-D76131A36494}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302A03C7-5B97-4B6F-B8E0-8596DE798D1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0705E85-70FB-4344-851D-558E56761DAD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6813,21 +6844,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302A03C7-5B97-4B6F-B8E0-8596DE798D1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F0855DB-26FE-4804-836B-D76131A36494}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>